--- a/CLP03N.xlsx
+++ b/CLP03N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="714" uniqueCount="270">
   <si>
     <t/>
   </si>
@@ -337,22 +337,16 @@
     <t>CMORY YOG.T&amp;C BLUE40</t>
   </si>
   <si>
-    <t>20115752</t>
-  </si>
-  <si>
-    <t>KIN YGR SLURP BLU 45</t>
-  </si>
-  <si>
-    <t>20115753</t>
-  </si>
-  <si>
-    <t>KIN YGR SLURP STR 45</t>
-  </si>
-  <si>
     <t>20124746</t>
   </si>
   <si>
     <t>S/N SS PRM SMK/BRT60</t>
+  </si>
+  <si>
+    <t>20141580</t>
+  </si>
+  <si>
+    <t>KIN YGR SLURP ORIG80</t>
   </si>
   <si>
     <t>20124744</t>
@@ -1219,7 +1213,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F120"/>
+  <dimension ref="A1:F119"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2103,10 +2097,10 @@
         <v>39</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>21</v>
+        <v>76</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -2123,7 +2117,7 @@
         <v>39</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>21</v>
@@ -2143,7 +2137,7 @@
         <v>39</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>76</v>
@@ -2160,13 +2154,13 @@
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>76</v>
+        <v>9</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -2183,7 +2177,7 @@
         <v>59</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>9</v>
@@ -2203,7 +2197,7 @@
         <v>59</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>9</v>
@@ -2223,7 +2217,7 @@
         <v>59</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>9</v>
@@ -2243,7 +2237,7 @@
         <v>59</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>9</v>
@@ -2263,10 +2257,10 @@
         <v>59</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>9</v>
+        <v>54</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -2283,7 +2277,7 @@
         <v>59</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>54</v>
@@ -2303,10 +2297,10 @@
         <v>59</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>54</v>
+        <v>9</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -2323,7 +2317,7 @@
         <v>59</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>9</v>
@@ -2340,10 +2334,10 @@
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>9</v>
@@ -2363,7 +2357,7 @@
         <v>62</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>9</v>
@@ -2383,7 +2377,7 @@
         <v>62</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>9</v>
@@ -2403,7 +2397,7 @@
         <v>62</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>9</v>
@@ -2423,7 +2417,7 @@
         <v>62</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>9</v>
@@ -2443,7 +2437,7 @@
         <v>62</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>9</v>
@@ -2463,7 +2457,7 @@
         <v>62</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>9</v>
@@ -2483,7 +2477,7 @@
         <v>62</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>9</v>
@@ -2500,10 +2494,10 @@
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>9</v>
@@ -2523,7 +2517,7 @@
         <v>65</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>9</v>
@@ -2543,7 +2537,7 @@
         <v>65</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>9</v>
@@ -2563,7 +2557,7 @@
         <v>65</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>9</v>
@@ -2583,7 +2577,7 @@
         <v>65</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>9</v>
@@ -2600,10 +2594,10 @@
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>9</v>
@@ -2611,19 +2605,19 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D70" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B70" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>162</v>
-      </c>
       <c r="E70" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>9</v>
@@ -2640,10 +2634,10 @@
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>9</v>
@@ -2660,10 +2654,10 @@
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>9</v>
@@ -2680,10 +2674,10 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>9</v>
@@ -2691,19 +2685,19 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D74" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="B74" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>171</v>
-      </c>
       <c r="E74" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>9</v>
@@ -2720,10 +2714,10 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>9</v>
@@ -2740,10 +2734,10 @@
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>9</v>
@@ -2760,10 +2754,10 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>9</v>
@@ -2780,10 +2774,10 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>9</v>
@@ -2800,10 +2794,10 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>9</v>
@@ -2811,19 +2805,19 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D80" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="B80" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>184</v>
-      </c>
       <c r="E80" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>9</v>
@@ -2840,10 +2834,10 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>9</v>
@@ -2860,10 +2854,10 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>9</v>
@@ -2880,10 +2874,10 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>9</v>
@@ -2900,10 +2894,10 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>9</v>
@@ -2920,10 +2914,10 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>9</v>
@@ -2940,7 +2934,7 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>39</v>
@@ -2960,33 +2954,33 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>9</v>
+        <v>199</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>59</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -3000,27 +2994,27 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>59</v>
+        <v>4</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>201</v>
+        <v>9</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D90" s="1" t="s">
         <v>204</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>206</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>4</v>
@@ -3040,10 +3034,10 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>9</v>
@@ -3060,10 +3054,10 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>9</v>
@@ -3080,10 +3074,10 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>9</v>
@@ -3100,10 +3094,10 @@
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>9</v>
@@ -3120,10 +3114,10 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>9</v>
@@ -3131,22 +3125,22 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D96" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="B96" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>219</v>
-      </c>
       <c r="E96" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>9</v>
+        <v>76</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -3160,13 +3154,13 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>76</v>
+        <v>9</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -3180,13 +3174,13 @@
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>9</v>
+        <v>76</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -3200,13 +3194,13 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>76</v>
+        <v>9</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -3220,10 +3214,10 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>9</v>
@@ -3240,10 +3234,10 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>9</v>
@@ -3260,10 +3254,10 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>9</v>
@@ -3280,10 +3274,10 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>9</v>
@@ -3300,10 +3294,10 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>9</v>
@@ -3311,19 +3305,19 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D105" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="B105" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="C105" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>238</v>
-      </c>
       <c r="E105" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>9</v>
@@ -3340,10 +3334,10 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>9</v>
@@ -3360,10 +3354,10 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>9</v>
@@ -3380,10 +3374,10 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>9</v>
@@ -3400,10 +3394,10 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>9</v>
@@ -3411,19 +3405,19 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D110" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="B110" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="C110" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>249</v>
-      </c>
       <c r="E110" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>9</v>
@@ -3440,10 +3434,10 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>9</v>
@@ -3460,10 +3454,10 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>9</v>
@@ -3480,10 +3474,10 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>9</v>
@@ -3491,19 +3485,19 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D114" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="B114" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="C114" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D114" s="1" t="s">
-        <v>258</v>
-      </c>
       <c r="E114" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>9</v>
@@ -3520,10 +3514,10 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>9</v>
@@ -3540,10 +3534,10 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>9</v>
@@ -3560,10 +3554,10 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>9</v>
@@ -3571,19 +3565,19 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D118" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="B118" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="C118" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D118" s="1" t="s">
-        <v>267</v>
-      </c>
       <c r="E118" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>9</v>
@@ -3600,32 +3594,12 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A120" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="B120" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="C120" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="E120" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F120" s="1" t="s">
         <v>9</v>
       </c>
     </row>
